--- a/地图表格/level7.xlsx
+++ b/地图表格/level7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\52724\SIMGame\SIMGame\地图表格\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2525720-8B29-49D8-A8E7-B736712F5125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6678A8-F7C6-4F7E-A7D4-93595A9457A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{384278E2-84AA-4801-85E0-EA8137CAFE39}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>出生点</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -81,10 +81,6 @@
   </si>
   <si>
     <t>光敏开关3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>机关锁2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -275,7 +271,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -294,9 +290,45 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -308,48 +340,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -673,8 +663,8 @@
   <sheetData>
     <row r="1" spans="1:50" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="X1" s="16" t="s">
-        <v>22</v>
+      <c r="X1" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="AA1" s="1"/>
       <c r="AN1" s="1"/>
@@ -683,39 +673,39 @@
     </row>
     <row r="2" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="AA2" s="21"/>
+      <c r="AA2" s="1"/>
       <c r="AN2" s="1"/>
       <c r="AO2" s="1"/>
       <c r="AX2" s="1"/>
     </row>
     <row r="3" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
-      <c r="AA3" s="21"/>
+      <c r="AA3" s="1"/>
       <c r="AN3" s="1"/>
       <c r="AO3" s="1"/>
       <c r="AX3" s="1"/>
     </row>
     <row r="4" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
-      <c r="AA4" s="21"/>
+      <c r="AA4" s="1"/>
       <c r="AN4" s="1"/>
       <c r="AO4" s="1"/>
       <c r="AX4" s="1"/>
     </row>
     <row r="5" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="AA5" s="21"/>
+      <c r="AA5" s="1"/>
       <c r="AN5" s="1"/>
       <c r="AO5" s="1"/>
       <c r="AX5" s="1"/>
     </row>
     <row r="6" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
-      <c r="AA6" s="20" t="s">
+      <c r="AA6" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM6" s="13" t="s">
         <v>20</v>
-      </c>
-      <c r="AM6" s="20" t="s">
-        <v>21</v>
       </c>
       <c r="AN6" s="1"/>
       <c r="AO6" s="1"/>
@@ -723,40 +713,40 @@
     </row>
     <row r="7" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
-      <c r="AA7" s="20"/>
-      <c r="AM7" s="20"/>
+      <c r="AA7" s="13"/>
+      <c r="AM7" s="13"/>
       <c r="AN7" s="1"/>
       <c r="AO7" s="1"/>
       <c r="AX7" s="1"/>
     </row>
     <row r="8" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
-      <c r="AA8" s="20"/>
-      <c r="AM8" s="20"/>
+      <c r="AA8" s="13"/>
+      <c r="AM8" s="13"/>
       <c r="AN8" s="1"/>
       <c r="AO8" s="1"/>
       <c r="AX8" s="1"/>
     </row>
     <row r="9" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="AA9" s="20"/>
-      <c r="AM9" s="20"/>
+      <c r="AA9" s="13"/>
+      <c r="AM9" s="13"/>
       <c r="AN9" s="1"/>
       <c r="AO9" s="1"/>
       <c r="AX9" s="1"/>
     </row>
     <row r="10" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="AA10" s="20"/>
-      <c r="AM10" s="20"/>
+      <c r="AA10" s="13"/>
+      <c r="AM10" s="13"/>
       <c r="AN10" s="1"/>
       <c r="AO10" s="1"/>
       <c r="AX10" s="1"/>
     </row>
     <row r="11" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="AA11" s="20"/>
-      <c r="AM11" s="20"/>
+      <c r="AA11" s="13"/>
+      <c r="AM11" s="13"/>
       <c r="AN11" s="1"/>
       <c r="AO11" s="1"/>
       <c r="AX11" s="1"/>
@@ -764,42 +754,39 @@
     <row r="12" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="G12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA12" s="20"/>
-      <c r="AM12" s="20"/>
+        <v>13</v>
+      </c>
+      <c r="AA12" s="13"/>
+      <c r="AM12" s="13"/>
       <c r="AN12" s="1"/>
       <c r="AO12" s="1"/>
       <c r="AX12" s="1"/>
     </row>
     <row r="13" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="V13" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="V13" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="W13" s="24"/>
-      <c r="X13" s="24"/>
-      <c r="Y13" s="24"/>
-      <c r="Z13" s="24"/>
+      <c r="W13" s="12"/>
+      <c r="X13" s="12"/>
+      <c r="Y13" s="12"/>
+      <c r="Z13" s="12"/>
       <c r="AA13" s="1"/>
-      <c r="AB13" s="10"/>
-      <c r="AC13" s="10"/>
-      <c r="AD13" s="10"/>
       <c r="AN13" s="1"/>
       <c r="AO13" s="1"/>
       <c r="AX13" s="1"/>
     </row>
     <row r="14" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="M14" s="23" t="s">
-        <v>30</v>
+      <c r="M14" s="11" t="s">
+        <v>29</v>
       </c>
       <c r="AA14" s="1"/>
       <c r="AN14" s="1"/>
@@ -822,11 +809,6 @@
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
-      <c r="V15" s="10"/>
-      <c r="W15" s="10"/>
-      <c r="X15" s="10"/>
-      <c r="Y15" s="10"/>
-      <c r="Z15" s="10"/>
       <c r="AA15" s="1"/>
       <c r="AN15" s="1"/>
       <c r="AO15" s="1"/>
@@ -834,11 +816,6 @@
     </row>
     <row r="16" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="V16" s="10"/>
-      <c r="W16" s="10"/>
-      <c r="X16" s="10"/>
-      <c r="Y16" s="10"/>
-      <c r="Z16" s="10"/>
       <c r="AA16" s="1"/>
       <c r="AN16" s="1"/>
       <c r="AO16" s="1"/>
@@ -846,11 +823,6 @@
     </row>
     <row r="17" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
-      <c r="V17" s="10"/>
-      <c r="W17" s="10"/>
-      <c r="X17" s="10"/>
-      <c r="Y17" s="10"/>
-      <c r="Z17" s="10"/>
       <c r="AA17" s="1"/>
       <c r="AN17" s="1"/>
       <c r="AO17" s="1"/>
@@ -858,11 +830,6 @@
     </row>
     <row r="18" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
-      <c r="V18" s="10"/>
-      <c r="W18" s="10"/>
-      <c r="X18" s="10"/>
-      <c r="Y18" s="10"/>
-      <c r="Z18" s="10"/>
       <c r="AA18" s="1"/>
       <c r="AN18" s="1"/>
       <c r="AO18" s="1"/>
@@ -874,11 +841,6 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
-      <c r="V19" s="10"/>
-      <c r="W19" s="10"/>
-      <c r="X19" s="10"/>
-      <c r="Y19" s="10"/>
-      <c r="Z19" s="10"/>
       <c r="AA19" s="1"/>
       <c r="AN19" s="1"/>
       <c r="AO19" s="1"/>
@@ -886,11 +848,6 @@
     </row>
     <row r="20" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
-      <c r="V20" s="10"/>
-      <c r="W20" s="10"/>
-      <c r="X20" s="10"/>
-      <c r="Y20" s="10"/>
-      <c r="Z20" s="10"/>
       <c r="AA20" s="1"/>
       <c r="AN20" s="1"/>
       <c r="AO20" s="1"/>
@@ -898,11 +855,6 @@
     </row>
     <row r="21" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
-      <c r="V21" s="10"/>
-      <c r="W21" s="10"/>
-      <c r="X21" s="10"/>
-      <c r="Y21" s="10"/>
-      <c r="Z21" s="10"/>
       <c r="AA21" s="1"/>
       <c r="AN21" s="1"/>
       <c r="AO21" s="1"/>
@@ -910,11 +862,6 @@
     </row>
     <row r="22" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
-      <c r="V22" s="10"/>
-      <c r="W22" s="10"/>
-      <c r="X22" s="10"/>
-      <c r="Y22" s="10"/>
-      <c r="Z22" s="10"/>
       <c r="AA22" s="1"/>
       <c r="AN22" s="1"/>
       <c r="AO22" s="1"/>
@@ -938,8 +885,6 @@
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
       <c r="U24" s="1"/>
-      <c r="V24" s="10"/>
-      <c r="W24" s="10"/>
       <c r="AA24" s="1"/>
       <c r="AN24" s="1"/>
       <c r="AO24" s="1"/>
@@ -950,11 +895,9 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="U25" s="1"/>
-      <c r="V25" s="10"/>
-      <c r="W25" s="10"/>
       <c r="AA25" s="1"/>
-      <c r="AD25" s="19" t="s">
-        <v>23</v>
+      <c r="AD25" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="AN25" s="1"/>
       <c r="AO25" s="1"/>
@@ -965,8 +908,6 @@
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="U26" s="1"/>
-      <c r="V26" s="10"/>
-      <c r="W26" s="10"/>
       <c r="AA26" s="1"/>
       <c r="AN26" s="1"/>
       <c r="AO26" s="1"/>
@@ -975,14 +916,12 @@
     <row r="27" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="U27" s="1"/>
-      <c r="V27" s="10"/>
-      <c r="W27" s="10"/>
       <c r="X27" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA27" s="1"/>
-      <c r="AL27" s="17" t="s">
-        <v>26</v>
+      <c r="AL27" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="AN27" s="1"/>
       <c r="AO27" s="1"/>
@@ -990,39 +929,33 @@
     </row>
     <row r="28" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
-      <c r="T28" s="10"/>
       <c r="U28" s="1"/>
-      <c r="V28" s="12" t="s">
+      <c r="V28" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="W28" s="17"/>
+      <c r="X28" s="17"/>
+      <c r="Y28" s="17"/>
+      <c r="Z28" s="17"/>
+      <c r="AA28" s="17"/>
+      <c r="AB28" s="17"/>
+      <c r="AC28" s="17"/>
+      <c r="AD28" s="17"/>
+      <c r="AE28" s="17"/>
+      <c r="AF28" s="17"/>
+      <c r="AI28" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="W28" s="12"/>
-      <c r="X28" s="12"/>
-      <c r="Y28" s="12"/>
-      <c r="Z28" s="12"/>
-      <c r="AA28" s="12"/>
-      <c r="AB28" s="12"/>
-      <c r="AC28" s="12"/>
-      <c r="AD28" s="12"/>
-      <c r="AE28" s="12"/>
-      <c r="AF28" s="12"/>
-      <c r="AG28" s="13"/>
-      <c r="AH28" s="13"/>
-      <c r="AI28" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="AJ28" s="12"/>
-      <c r="AK28" s="12"/>
-      <c r="AL28" s="12"/>
-      <c r="AM28" s="12"/>
-      <c r="AN28" s="12"/>
-      <c r="AO28" s="12"/>
-      <c r="AP28" s="12"/>
-      <c r="AQ28" s="12"/>
-      <c r="AR28" s="12"/>
-      <c r="AS28" s="12"/>
-      <c r="AT28" s="13"/>
-      <c r="AU28" s="13"/>
-      <c r="AV28" s="13"/>
+      <c r="AJ28" s="17"/>
+      <c r="AK28" s="17"/>
+      <c r="AL28" s="17"/>
+      <c r="AM28" s="17"/>
+      <c r="AN28" s="17"/>
+      <c r="AO28" s="17"/>
+      <c r="AP28" s="17"/>
+      <c r="AQ28" s="17"/>
+      <c r="AR28" s="17"/>
+      <c r="AS28" s="17"/>
       <c r="AX28" s="1"/>
     </row>
     <row r="29" spans="1:50" x14ac:dyDescent="0.3">
@@ -1054,7 +987,6 @@
     </row>
     <row r="32" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
-      <c r="X32" s="10"/>
       <c r="AA32" s="1"/>
       <c r="AN32" s="1"/>
       <c r="AO32" s="1"/>
@@ -1082,7 +1014,7 @@
     </row>
     <row r="34" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
-      <c r="S34" s="12" t="s">
+      <c r="S34" s="17" t="s">
         <v>9</v>
       </c>
       <c r="AA34" s="1"/>
@@ -1092,9 +1024,9 @@
     </row>
     <row r="35" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
-      <c r="S35" s="12"/>
+      <c r="S35" s="17"/>
       <c r="AA35" s="1"/>
-      <c r="AI35" s="11" t="s">
+      <c r="AI35" s="6" t="s">
         <v>11</v>
       </c>
       <c r="AN35" s="1"/>
@@ -1103,9 +1035,9 @@
     </row>
     <row r="36" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
-      <c r="S36" s="12"/>
-      <c r="W36" s="11" t="s">
-        <v>15</v>
+      <c r="S36" s="17"/>
+      <c r="W36" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="AA36" s="1"/>
       <c r="AN36" s="1"/>
@@ -1142,7 +1074,7 @@
     </row>
     <row r="38" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
-      <c r="Q38" s="9" t="s">
+      <c r="V38" s="21" t="s">
         <v>7</v>
       </c>
       <c r="AA38" s="1"/>
@@ -1155,7 +1087,7 @@
     </row>
     <row r="39" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
-      <c r="Q39" s="9"/>
+      <c r="V39" s="21"/>
       <c r="AA39" s="1"/>
       <c r="AN39" s="1"/>
       <c r="AO39" s="1"/>
@@ -1163,10 +1095,8 @@
     </row>
     <row r="40" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
-      <c r="Q40" s="9"/>
-      <c r="V40" s="5" t="s">
-        <v>12</v>
-      </c>
+      <c r="S40" s="5"/>
+      <c r="V40" s="21"/>
       <c r="AA40" s="1"/>
       <c r="AN40" s="1"/>
       <c r="AO40" s="1"/>
@@ -1174,15 +1104,9 @@
     </row>
     <row r="41" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
@@ -1194,8 +1118,8 @@
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
       <c r="X41" s="1"/>
-      <c r="Y41" s="1"/>
-      <c r="Z41" s="1"/>
+      <c r="Y41" s="22"/>
+      <c r="Z41" s="22"/>
       <c r="AA41" s="1"/>
       <c r="AN41" s="1"/>
       <c r="AO41" s="1"/>
@@ -1203,7 +1127,7 @@
     </row>
     <row r="42" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
-      <c r="O42" s="8" t="s">
+      <c r="O42" s="20" t="s">
         <v>5</v>
       </c>
       <c r="AA42" s="1"/>
@@ -1213,7 +1137,7 @@
     </row>
     <row r="43" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
-      <c r="O43" s="8"/>
+      <c r="O43" s="20"/>
       <c r="AA43" s="1"/>
       <c r="AD43" s="5" t="s">
         <v>10</v>
@@ -1227,7 +1151,7 @@
       <c r="D44" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="O44" s="8"/>
+      <c r="O44" s="20"/>
       <c r="U44" s="4" t="s">
         <v>6</v>
       </c>
@@ -1266,70 +1190,70 @@
       <c r="A46" s="1"/>
       <c r="M46" s="1"/>
       <c r="AA46" s="1"/>
-      <c r="AN46" s="15" t="s">
-        <v>18</v>
+      <c r="AN46" s="14" t="s">
+        <v>17</v>
       </c>
       <c r="AO46" s="1"/>
       <c r="AX46" s="1"/>
     </row>
     <row r="47" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
-      <c r="M47" s="7" t="s">
+      <c r="M47" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="AA47" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="AN47" s="15"/>
-      <c r="AO47" s="18" t="s">
-        <v>27</v>
+      <c r="AA47" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="AN47" s="14"/>
+      <c r="AO47" s="16" t="s">
+        <v>26</v>
       </c>
       <c r="AX47" s="1"/>
     </row>
     <row r="48" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D48" s="6"/>
-      <c r="M48" s="7"/>
-      <c r="S48" s="6" t="s">
+      <c r="D48" s="15"/>
+      <c r="M48" s="19"/>
+      <c r="S48" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="T48" s="6"/>
-      <c r="AA48" s="22"/>
-      <c r="AL48" s="6" t="s">
+      <c r="T48" s="15"/>
+      <c r="AA48" s="18"/>
+      <c r="AL48" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="AM48" s="6"/>
-      <c r="AN48" s="15"/>
-      <c r="AO48" s="18"/>
-      <c r="AS48" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AT48" s="6"/>
+      <c r="AM48" s="15"/>
+      <c r="AN48" s="14"/>
+      <c r="AO48" s="16"/>
+      <c r="AS48" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="AT48" s="15"/>
       <c r="AX48" s="1"/>
     </row>
     <row r="49" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="15"/>
       <c r="H49" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M49" s="7"/>
-      <c r="S49" s="6"/>
-      <c r="T49" s="6"/>
-      <c r="AA49" s="22"/>
-      <c r="AG49" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL49" s="6"/>
-      <c r="AM49" s="6"/>
-      <c r="AN49" s="15"/>
-      <c r="AO49" s="18"/>
-      <c r="AS49" s="6"/>
-      <c r="AT49" s="6"/>
+        <v>12</v>
+      </c>
+      <c r="M49" s="19"/>
+      <c r="S49" s="15"/>
+      <c r="T49" s="15"/>
+      <c r="AA49" s="18"/>
+      <c r="AG49" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL49" s="15"/>
+      <c r="AM49" s="15"/>
+      <c r="AN49" s="14"/>
+      <c r="AO49" s="16"/>
+      <c r="AS49" s="15"/>
+      <c r="AT49" s="15"/>
       <c r="AX49" s="1"/>
     </row>
     <row r="50" spans="1:50" x14ac:dyDescent="0.3">
@@ -1386,23 +1310,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="C48:D49"/>
+    <mergeCell ref="S48:T49"/>
+    <mergeCell ref="M47:M49"/>
+    <mergeCell ref="AL48:AM49"/>
+    <mergeCell ref="O42:O44"/>
+    <mergeCell ref="AS48:AT49"/>
+    <mergeCell ref="AO47:AO49"/>
+    <mergeCell ref="V28:AF28"/>
+    <mergeCell ref="AI28:AS28"/>
+    <mergeCell ref="AA47:AA49"/>
     <mergeCell ref="E13:I13"/>
     <mergeCell ref="V13:Z13"/>
     <mergeCell ref="AA6:AA12"/>
     <mergeCell ref="AM6:AM12"/>
     <mergeCell ref="AN46:AN49"/>
-    <mergeCell ref="AS48:AT49"/>
-    <mergeCell ref="AO47:AO49"/>
-    <mergeCell ref="V28:AF28"/>
-    <mergeCell ref="AI28:AS28"/>
-    <mergeCell ref="AA47:AA49"/>
     <mergeCell ref="S34:S36"/>
-    <mergeCell ref="C48:D49"/>
-    <mergeCell ref="S48:T49"/>
-    <mergeCell ref="M47:M49"/>
-    <mergeCell ref="AL48:AM49"/>
-    <mergeCell ref="O42:O44"/>
-    <mergeCell ref="Q38:Q40"/>
+    <mergeCell ref="V38:V40"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
